--- a/artfynd/A 40255-2023 artfynd.xlsx
+++ b/artfynd/A 40255-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40255-2023 artfynd.xlsx
+++ b/artfynd/A 40255-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80748340</v>
+        <v>80748312</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352750.19031887</v>
+        <v>352706</v>
       </c>
       <c r="R2" t="n">
-        <v>6367344.189990521</v>
+        <v>6367306</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -748,24 +743,14 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>revlummer 2 m2</t>
+          <t>Revlummer 2x2m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80748330</v>
+        <v>80748321</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>352690.8710355927</v>
+        <v>352752</v>
       </c>
       <c r="R3" t="n">
-        <v>6367406.15035022</v>
+        <v>6367343</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -865,24 +845,14 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>revlummer 5 m2</t>
+          <t>Revlummer 2x2 m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80748342</v>
+        <v>80748330</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>352705.7272025679</v>
+        <v>352691</v>
       </c>
       <c r="R4" t="n">
-        <v>6367428.786940325</v>
+        <v>6367406</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -982,24 +947,14 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>revlummer 1 m2</t>
+          <t>revlummer 5 m2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80748321</v>
+        <v>80748340</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>352751.7692671136</v>
+        <v>352750</v>
       </c>
       <c r="R5" t="n">
-        <v>6367343.055178222</v>
+        <v>6367344</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1099,24 +1049,14 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Revlummer 2x2 m</t>
+          <t>revlummer 2 m2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,6 +1080,210 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>80748341</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bäckäng, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>352761</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6367367</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Surteby-Kattunga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>revlummer 1 m2</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Malin Stensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Malin Stensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>80748342</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bäckäng, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>352706</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6367429</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Surteby-Kattunga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>revlummer 1 m2</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Malin Stensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Malin Stensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
